--- a/poker/resources/sample/Cumulativebenefits.xlsx
+++ b/poker/resources/sample/Cumulativebenefits.xlsx
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="41">
   <si>
     <t>序列ID</t>
   </si>
@@ -212,6 +212,9 @@
   </si>
   <si>
     <t>1990000_40000000</t>
+  </si>
+  <si>
+    <t>1990000_50000000</t>
   </si>
   <si>
     <t>阶段奖励1</t>
@@ -1415,7 +1418,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9.625" style="1" customWidth="1"/>
@@ -1872,25 +1875,27 @@
     </row>
     <row r="24" s="2" customFormat="1" spans="1:6">
       <c r="A24" s="2">
-        <v>2001</v>
+        <v>1020</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="2">
+        <v>1</v>
+      </c>
+      <c r="D24" s="2">
+        <v>4</v>
+      </c>
+      <c r="E24" s="2">
+        <v>50000</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="C24" s="2">
-        <v>2</v>
-      </c>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2">
-        <v>1000</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" spans="1:6">
       <c r="A25" s="2">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>37</v>
@@ -1898,16 +1903,17 @@
       <c r="C25" s="2">
         <v>2</v>
       </c>
+      <c r="D25" s="2"/>
       <c r="E25" s="2">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" spans="1:6">
       <c r="A26" s="2">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>38</v>
@@ -1916,10 +1922,27 @@
         <v>2</v>
       </c>
       <c r="E26" s="2">
+        <v>10000</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" spans="1:6">
+      <c r="A27" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="2">
+        <v>2</v>
+      </c>
+      <c r="E27" s="2">
         <v>100000</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>39</v>
+      <c r="F27" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/Cumulativebenefits.xlsx
+++ b/poker/resources/sample/Cumulativebenefits.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet name="Cumulativebenefits" sheetId="1" r:id="rId1"/>
+    <sheet name="Cumulativebenefits" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,29 +32,6 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-相同任务类型，在当前时间下，任务组ID只会读取一个进行显示
-</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="E1" authorId="0">
       <text>
         <r>
@@ -73,29 +50,9 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-任务需要充值的金额</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-达成条件所得奖励</t>
+1.达成任务所需要的条件以及奖励的道具和数量
+2.说明：任务类型1-5代表每一天开启的任务活动，是按照权重进行抽取开启，每个任务类型最多配置4条充值任务；
+</t>
         </r>
       </text>
     </comment>
@@ -104,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>序列ID</t>
   </si>
@@ -115,19 +72,16 @@
     <t>类型</t>
   </si>
   <si>
-    <t>任务组</t>
-  </si>
-  <si>
-    <t>达成条件</t>
-  </si>
-  <si>
-    <t>道具ID_道具数量</t>
+    <t>权重</t>
+  </si>
+  <si>
+    <t>任务条件_道具ID_道具数量</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
-    <t>map&lt;int{_}long&gt;{;}</t>
+    <t>map&lt;int{,}list&lt;long&gt;{_}&gt;{|}</t>
   </si>
   <si>
     <t>id</t>
@@ -136,97 +90,46 @@
     <t>type</t>
   </si>
   <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>condition</t>
+    <t>weight</t>
   </si>
   <si>
     <t>rewards</t>
   </si>
   <si>
-    <t>任务1</t>
-  </si>
-  <si>
-    <t>1990000_10000</t>
-  </si>
-  <si>
-    <t>1990000_20000</t>
-  </si>
-  <si>
-    <t>1990000_30000</t>
-  </si>
-  <si>
-    <t>1990000_40000</t>
-  </si>
-  <si>
-    <t>1990000_50000</t>
-  </si>
-  <si>
-    <t>任务2</t>
-  </si>
-  <si>
-    <t>1990000_100000</t>
-  </si>
-  <si>
-    <t>1990000_200000</t>
-  </si>
-  <si>
-    <t>1990000_300000</t>
-  </si>
-  <si>
-    <t>1990000_400000</t>
-  </si>
-  <si>
-    <t>1990000_500000</t>
-  </si>
-  <si>
-    <t>任务3</t>
-  </si>
-  <si>
-    <t>1990000_1000000</t>
-  </si>
-  <si>
-    <t>1990000_2000000</t>
-  </si>
-  <si>
-    <t>1990000_3000000</t>
-  </si>
-  <si>
-    <t>1990000_4000000</t>
-  </si>
-  <si>
-    <t>1990000_5000000</t>
-  </si>
-  <si>
-    <t>任务4</t>
-  </si>
-  <si>
-    <t>1990000_10000000</t>
-  </si>
-  <si>
-    <t>1990000_20000000</t>
-  </si>
-  <si>
-    <t>1990000_30000000</t>
-  </si>
-  <si>
-    <t>1990000_40000000</t>
-  </si>
-  <si>
-    <t>1990000_50000000</t>
+    <t>任务类型1</t>
+  </si>
+  <si>
+    <t>10,1990000_10000|100,1990000,100000|1000,1990000_1000000|10000,1990000_10000000</t>
+  </si>
+  <si>
+    <t>任务类型2</t>
+  </si>
+  <si>
+    <t>任务类型3</t>
+  </si>
+  <si>
+    <t>任务类型4</t>
+  </si>
+  <si>
+    <t>任务类型5</t>
   </si>
   <si>
     <t>阶段奖励1</t>
   </si>
   <si>
+    <t>1000,1990000_5000000</t>
+  </si>
+  <si>
     <t>阶段奖励2</t>
   </si>
   <si>
+    <t>10000,1990000_10000000</t>
+  </si>
+  <si>
     <t>阶段奖励3</t>
   </si>
   <si>
-    <t>1990000_100000000</t>
+    <t>100000,1990000_100000000</t>
   </si>
 </sst>
 </file>
@@ -870,7 +773,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -881,6 +784,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1418,18 +1324,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="9.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="11" style="1" customWidth="1"/>
     <col min="3" max="3" width="5.5" style="1" customWidth="1"/>
-    <col min="4" max="5" width="14.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.625" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="14.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="91.875" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1445,75 +1351,62 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:5">
+      <c r="A2" s="3" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:6">
-      <c r="A2" s="3" t="s">
-        <v>6</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="1" t="s">
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:5">
+      <c r="A3" s="3" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:6">
-      <c r="A3" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>12</v>
-      </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:6">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+    <row r="4" s="1" customFormat="1" spans="1:5">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:6">
+    <row r="5" s="1" customFormat="1" spans="1:5">
       <c r="A5" s="2">
         <v>1001</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
       </c>
       <c r="D5" s="2">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2">
-        <v>10</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>14</v>
+        <v>5</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:6">
+    <row r="6" s="2" customFormat="1" spans="1:5">
       <c r="A6" s="2">
         <v>1002</v>
       </c>
@@ -1524,61 +1417,52 @@
         <v>1</v>
       </c>
       <c r="D6" s="2">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2">
-        <v>20</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>15</v>
+        <v>4</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:6">
+    <row r="7" s="2" customFormat="1" spans="1:5">
       <c r="A7" s="2">
         <v>1003</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
       </c>
       <c r="D7" s="2">
-        <v>1</v>
-      </c>
-      <c r="E7" s="2">
-        <v>30</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>16</v>
+        <v>3</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:6">
+    <row r="8" s="2" customFormat="1" spans="1:5">
       <c r="A8" s="2">
         <v>1004</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C8" s="2">
         <v>1</v>
       </c>
       <c r="D8" s="2">
-        <v>1</v>
-      </c>
-      <c r="E8" s="2">
-        <v>40</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>17</v>
+        <v>2</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" spans="1:6">
+    <row r="9" s="2" customFormat="1" spans="1:5">
       <c r="A9" s="2">
         <v>1005</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
@@ -1586,369 +1470,79 @@
       <c r="D9" s="2">
         <v>1</v>
       </c>
-      <c r="E9" s="2">
-        <v>50</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="E9" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" spans="1:5">
+      <c r="A10" s="2">
+        <v>2001</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" spans="1:6">
-      <c r="A10" s="2">
-        <v>1006</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="2">
-        <v>1</v>
-      </c>
-      <c r="D10" s="2">
-        <v>2</v>
-      </c>
-      <c r="E10" s="2">
-        <v>100</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" spans="1:6">
+    <row r="11" s="2" customFormat="1" spans="1:5">
       <c r="A11" s="2">
-        <v>1007</v>
+        <v>2002</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="2">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2">
         <v>2</v>
       </c>
-      <c r="E11" s="2">
-        <v>200</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" spans="1:5">
+      <c r="A12" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="1:6">
-      <c r="A12" s="2">
-        <v>1008</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="C12" s="2">
-        <v>1</v>
-      </c>
-      <c r="D12" s="2">
         <v>2</v>
       </c>
-      <c r="E12" s="2">
-        <v>300</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="D12" s="2"/>
+      <c r="E12" s="2" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" spans="1:6">
-      <c r="A13" s="2">
-        <v>1009</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="2">
-        <v>1</v>
-      </c>
-      <c r="D13" s="2">
-        <v>2</v>
-      </c>
-      <c r="E13" s="2">
-        <v>400</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="1:6">
-      <c r="A14" s="2">
-        <v>1010</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="2">
-        <v>1</v>
-      </c>
-      <c r="D14" s="2">
-        <v>2</v>
-      </c>
-      <c r="E14" s="2">
-        <v>500</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="1:6">
-      <c r="A15" s="2">
-        <v>1011</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="2">
-        <v>1</v>
-      </c>
-      <c r="D15" s="2">
-        <v>3</v>
-      </c>
-      <c r="E15" s="2">
-        <v>1000</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="1:6">
-      <c r="A16" s="2">
-        <v>1012</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="2">
-        <v>1</v>
-      </c>
-      <c r="D16" s="2">
-        <v>3</v>
-      </c>
-      <c r="E16" s="2">
-        <v>2000</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="1:6">
-      <c r="A17" s="2">
-        <v>1013</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="2">
-        <v>1</v>
-      </c>
-      <c r="D17" s="2">
-        <v>3</v>
-      </c>
-      <c r="E17" s="2">
-        <v>3000</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="1:6">
-      <c r="A18" s="2">
-        <v>1014</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="2">
-        <v>1</v>
-      </c>
-      <c r="D18" s="2">
-        <v>3</v>
-      </c>
-      <c r="E18" s="2">
-        <v>4000</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="1:6">
-      <c r="A19" s="2">
-        <v>1015</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="2">
-        <v>1</v>
-      </c>
-      <c r="D19" s="2">
-        <v>3</v>
-      </c>
-      <c r="E19" s="2">
-        <v>5000</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="1:6">
-      <c r="A20" s="2">
-        <v>1016</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="2">
-        <v>1</v>
-      </c>
-      <c r="D20" s="2">
-        <v>4</v>
-      </c>
-      <c r="E20" s="2">
-        <v>10000</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="1:6">
-      <c r="A21" s="2">
-        <v>1017</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="2">
-        <v>1</v>
-      </c>
-      <c r="D21" s="2">
-        <v>4</v>
-      </c>
-      <c r="E21" s="2">
-        <v>20000</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" spans="1:6">
-      <c r="A22" s="2">
-        <v>1018</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="2">
-        <v>1</v>
-      </c>
-      <c r="D22" s="2">
-        <v>4</v>
-      </c>
-      <c r="E22" s="2">
-        <v>30000</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" spans="1:6">
-      <c r="A23" s="2">
-        <v>1019</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="2">
-        <v>1</v>
-      </c>
-      <c r="D23" s="2">
-        <v>4</v>
-      </c>
-      <c r="E23" s="2">
-        <v>40000</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" spans="1:6">
-      <c r="A24" s="2">
-        <v>1020</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="2">
-        <v>1</v>
-      </c>
-      <c r="D24" s="2">
-        <v>4</v>
-      </c>
-      <c r="E24" s="2">
-        <v>50000</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" spans="1:6">
-      <c r="A25" s="2">
-        <v>2001</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="2">
-        <v>2</v>
-      </c>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2">
-        <v>1000</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" spans="1:6">
-      <c r="A26" s="2">
-        <v>2002</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C26" s="2">
-        <v>2</v>
-      </c>
-      <c r="E26" s="2">
-        <v>10000</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="1:6">
-      <c r="A27" s="2">
-        <v>2003</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" s="2">
-        <v>2</v>
-      </c>
-      <c r="E27" s="2">
-        <v>100000</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F2">
+  <conditionalFormatting sqref="E5">
+    <cfRule type="expression" dxfId="0" priority="6">
+      <formula>MOD($B5,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>MOD($B6,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7">
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>MOD($B7,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>MOD($B8,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>MOD($B2,2)=1</formula>
+      <formula>MOD($B9,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/poker/resources/sample/Cumulativebenefits.xlsx
+++ b/poker/resources/sample/Cumulativebenefits.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
   <si>
     <t>序列ID</t>
   </si>
@@ -99,19 +99,31 @@
     <t>任务类型1</t>
   </si>
   <si>
-    <t>10,1990000_10000|100,1990000,100000|1000,1990000_1000000|10000,1990000_10000000</t>
+    <t>10,1990000_10000|100,1990000_100000|1000,1990000_1000000|10000,1990000_10000000</t>
   </si>
   <si>
     <t>任务类型2</t>
   </si>
   <si>
+    <t>20,1990000_20000|200,1990000_200000|2000,1990000_2000000|20000,1990000_20000000</t>
+  </si>
+  <si>
     <t>任务类型3</t>
   </si>
   <si>
+    <t>30,1990000_30000|300,1990000_300000|3000,1990000_3000000|30000,1990000_30000000</t>
+  </si>
+  <si>
     <t>任务类型4</t>
   </si>
   <si>
+    <t>40,1990000_40000|400,1990000_400000|4000,1990000_4000000|40000,1990000_40000000</t>
+  </si>
+  <si>
     <t>任务类型5</t>
+  </si>
+  <si>
+    <t>50,1990000_50000|500,1990000_500000|5000,1990000_5000000|50000,1990000_50000000</t>
   </si>
   <si>
     <t>阶段奖励1</t>
@@ -773,7 +785,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -784,9 +796,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1331,7 +1340,7 @@
     <col min="2" max="2" width="11" style="1" customWidth="1"/>
     <col min="3" max="3" width="5.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="91.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24.875" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1378,7 +1387,7 @@
       <c r="D3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1420,7 +1429,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" spans="1:5">
@@ -1428,7 +1437,7 @@
         <v>1003</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
@@ -1437,7 +1446,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:5">
@@ -1445,7 +1454,7 @@
         <v>1004</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C8" s="2">
         <v>1</v>
@@ -1454,7 +1463,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" spans="1:5">
@@ -1462,7 +1471,7 @@
         <v>1005</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
@@ -1471,7 +1480,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" spans="1:5">
@@ -1479,14 +1488,14 @@
         <v>2001</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C10" s="2">
         <v>2</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" spans="1:5">
@@ -1494,14 +1503,14 @@
         <v>2002</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C11" s="2">
         <v>2</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:5">
@@ -1509,40 +1518,20 @@
         <v>2003</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C12" s="2">
         <v>2</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="0" priority="6">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>MOD($B5,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="0" priority="4">
-      <formula>MOD($B6,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="0" priority="3">
-      <formula>MOD($B7,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>MOD($B8,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>MOD($B9,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/poker/resources/sample/Cumulativebenefits.xlsx
+++ b/poker/resources/sample/Cumulativebenefits.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\activity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1014BE-DF45-4C34-BED7-3752F9D0DB5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73291292-6D5F-4D88-BBAC-8D097350126F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
